--- a/doanmon/FILE_LOI_6_MOT_PHAN_DUNG_MOT_PHAN_SAI.xlsx
+++ b/doanmon/FILE_LOI_6_MOT_PHAN_DUNG_MOT_PHAN_SAI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>productCode</t>
   </si>
@@ -35,10 +35,10 @@
     <t>CAKE-GOOD-001</t>
   </si>
   <si>
-    <t>Perfect Chocolate Cake</t>
-  </si>
-  <si>
-    <t>Chocolate</t>
+    <t>Perfect Birthday Cake</t>
+  </si>
+  <si>
+    <t>Birthday Cakes</t>
   </si>
   <si>
     <t>This row is completely valid</t>
@@ -53,7 +53,7 @@
     <t/>
   </si>
   <si>
-    <t>Vanilla</t>
+    <t>Wedding Cakes</t>
   </si>
   <si>
     <t>ERROR: price is empty</t>
@@ -62,10 +62,10 @@
     <t>CAKE-GOOD-002</t>
   </si>
   <si>
-    <t>Strawberry Delight</t>
-  </si>
-  <si>
-    <t>Fruit</t>
+    <t>Cheesecake Delight</t>
+  </si>
+  <si>
+    <t>Cheese Cakes</t>
   </si>
   <si>
     <t>This row is valid</t>
@@ -86,7 +86,10 @@
     <t>CAKE-GOOD-003</t>
   </si>
   <si>
-    <t>Vanilla Supreme</t>
+    <t>Gataux Supreme</t>
+  </si>
+  <si>
+    <t>Gataux</t>
   </si>
   <si>
     <t>CAKE-BAD-003</t>
@@ -101,7 +104,7 @@
     <t>CAKE-GOOD-004</t>
   </si>
   <si>
-    <t>Blueberry Cake</t>
+    <t>Wedding Cake Special</t>
   </si>
   <si>
     <t>CAKE-BAD-004</t>
@@ -113,7 +116,7 @@
     <t>CAKE-GOOD-005</t>
   </si>
   <si>
-    <t>Lemon Tart</t>
+    <t>Opera Gataux</t>
   </si>
   <si>
     <t>CAKE-BAD-005</t>
@@ -190,7 +193,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="14.58984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="18.5703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="17.6484375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="5.46875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="13.75" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="8.44140625" customWidth="true" bestFit="true"/>
@@ -225,7 +228,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>25.99</v>
+        <v>35.99</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>8</v>
@@ -265,7 +268,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>22.5</v>
+        <v>28.5</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>17</v>
@@ -305,10 +308,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>19.99</v>
+        <v>45.99</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n" s="0">
         <v>35.0</v>
@@ -319,10 +322,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>24.5</v>
@@ -334,24 +337,24 @@
         <v>-10.0</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>21.99</v>
+        <v>175.0</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>45.0</v>
+        <v>8.0</v>
       </c>
       <c r="F8" t="s" s="0">
         <v>18</v>
@@ -359,7 +362,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>12</v>
@@ -368,27 +371,27 @@
         <v>29.99</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n" s="0">
         <v>20.0</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>17.5</v>
+        <v>48.5</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E10" t="n" s="0">
         <v>30.0</v>
@@ -399,22 +402,22 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n" s="0">
         <v>15.0</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
